--- a/assets/calculateur-prix-depart-fr.xlsx
+++ b/assets/calculateur-prix-depart-fr.xlsx
@@ -37,16 +37,16 @@
     <t>Taux de marge souhaité</t>
   </si>
   <si>
-    <t>TVA</t>
+    <t>Taxes de vente (TPS + TVQ)</t>
   </si>
   <si>
     <t>Coût de revient</t>
   </si>
   <si>
-    <t>Prix de vente HT</t>
-  </si>
-  <si>
-    <t>Prix de vente TTC</t>
+    <t>Prix de vente avant taxes</t>
+  </si>
+  <si>
+    <t>Prix de vente taxes incluses</t>
   </si>
   <si>
     <t>Bénéfice par produit</t>
@@ -494,7 +494,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>0.2</v>
+        <v>0.14975</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
